--- a/MML_Study_Plan_v4.xlsx
+++ b/MML_Study_Plan_v4.xlsx
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="C5" s="42" t="n">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -1760,11 +1760,11 @@
         </is>
       </c>
       <c r="C6" s="42" t="n">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1826,11 +1826,11 @@
         </is>
       </c>
       <c r="C7" s="43" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1892,11 +1892,11 @@
         </is>
       </c>
       <c r="C8" s="43" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -1958,11 +1958,11 @@
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2024,11 +2024,11 @@
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2090,11 +2090,11 @@
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -2156,11 +2156,11 @@
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>46170</v>
+        <v>46172</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2226,11 +2226,11 @@
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2296,11 +2296,11 @@
         </is>
       </c>
       <c r="C14" s="43" t="n">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -2366,11 +2366,11 @@
         </is>
       </c>
       <c r="C15" s="43" t="n">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -2436,11 +2436,11 @@
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2506,11 +2506,11 @@
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2576,11 +2576,11 @@
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2646,11 +2646,11 @@
         </is>
       </c>
       <c r="C19" s="42" t="n">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2712,11 +2712,11 @@
         </is>
       </c>
       <c r="C20" s="42" t="n">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2782,11 +2782,11 @@
         </is>
       </c>
       <c r="C21" s="43" t="n">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -2852,11 +2852,11 @@
         </is>
       </c>
       <c r="C22" s="43" t="n">
-        <v>46180</v>
+        <v>46182</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -2922,11 +2922,11 @@
         </is>
       </c>
       <c r="C23" s="44" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="C24" s="44" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -3044,11 +3044,11 @@
         </is>
       </c>
       <c r="C25" s="44" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3096,11 +3096,11 @@
         </is>
       </c>
       <c r="C26" s="44" t="n">
-        <v>46184</v>
+        <v>46186</v>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -3152,11 +3152,11 @@
         </is>
       </c>
       <c r="C27" s="44" t="n">
-        <v>46185</v>
+        <v>46187</v>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3208,11 +3208,11 @@
         </is>
       </c>
       <c r="C28" s="45" t="n">
-        <v>46186</v>
+        <v>46188</v>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -3264,11 +3264,11 @@
         </is>
       </c>
       <c r="C29" s="45" t="n">
-        <v>46187</v>
+        <v>46189</v>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -3320,11 +3320,11 @@
         </is>
       </c>
       <c r="C30" s="46" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -3376,11 +3376,11 @@
         </is>
       </c>
       <c r="C31" s="46" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -3428,11 +3428,11 @@
         </is>
       </c>
       <c r="C32" s="46" t="n">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -3480,11 +3480,11 @@
         </is>
       </c>
       <c r="C33" s="46" t="n">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -3532,11 +3532,11 @@
         </is>
       </c>
       <c r="C34" s="46" t="n">
-        <v>46192</v>
+        <v>46194</v>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -3584,11 +3584,11 @@
         </is>
       </c>
       <c r="C35" s="47" t="n">
-        <v>46193</v>
+        <v>46195</v>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -3636,11 +3636,11 @@
         </is>
       </c>
       <c r="C36" s="47" t="n">
-        <v>46194</v>
+        <v>46196</v>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -3688,11 +3688,11 @@
         </is>
       </c>
       <c r="C37" s="46" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="D37" s="17" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3744,11 +3744,11 @@
         </is>
       </c>
       <c r="C38" s="46" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3800,11 +3800,11 @@
         </is>
       </c>
       <c r="C39" s="46" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="D39" s="17" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3856,11 +3856,11 @@
         </is>
       </c>
       <c r="C40" s="46" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3912,11 +3912,11 @@
         </is>
       </c>
       <c r="C41" s="46" t="n">
-        <v>46199</v>
+        <v>46201</v>
       </c>
       <c r="D41" s="17" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3968,11 +3968,11 @@
         </is>
       </c>
       <c r="C42" s="47" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
@@ -4024,11 +4024,11 @@
         </is>
       </c>
       <c r="C43" s="47" t="n">
-        <v>46201</v>
+        <v>46203</v>
       </c>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
@@ -4080,11 +4080,11 @@
         </is>
       </c>
       <c r="C44" s="48" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="D44" s="21" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -4136,11 +4136,11 @@
         </is>
       </c>
       <c r="C45" s="48" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="D45" s="21" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -4188,11 +4188,11 @@
         </is>
       </c>
       <c r="C46" s="48" t="n">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="D46" s="21" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -4240,11 +4240,11 @@
         </is>
       </c>
       <c r="C47" s="48" t="n">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="D47" s="21" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -4292,11 +4292,11 @@
         </is>
       </c>
       <c r="C48" s="48" t="n">
-        <v>46206</v>
+        <v>46208</v>
       </c>
       <c r="D48" s="21" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -4344,11 +4344,11 @@
         </is>
       </c>
       <c r="C49" s="49" t="n">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="D49" s="23" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
@@ -4396,11 +4396,11 @@
         </is>
       </c>
       <c r="C50" s="49" t="n">
-        <v>46208</v>
+        <v>46210</v>
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
@@ -4448,11 +4448,11 @@
         </is>
       </c>
       <c r="C51" s="48" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="D51" s="21" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -4504,11 +4504,11 @@
         </is>
       </c>
       <c r="C52" s="48" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="D52" s="21" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="C53" s="48" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -4616,11 +4616,11 @@
         </is>
       </c>
       <c r="C54" s="48" t="n">
-        <v>46212</v>
+        <v>46214</v>
       </c>
       <c r="D54" s="21" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -4672,11 +4672,11 @@
         </is>
       </c>
       <c r="C55" s="48" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="D55" s="21" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -4728,11 +4728,11 @@
         </is>
       </c>
       <c r="C56" s="49" t="n">
-        <v>46214</v>
+        <v>46216</v>
       </c>
       <c r="D56" s="23" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
@@ -4784,11 +4784,11 @@
         </is>
       </c>
       <c r="C57" s="49" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="D57" s="23" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
@@ -4840,11 +4840,11 @@
         </is>
       </c>
       <c r="C58" s="50" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -4896,11 +4896,11 @@
         </is>
       </c>
       <c r="C59" s="50" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -4948,11 +4948,11 @@
         </is>
       </c>
       <c r="C60" s="50" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -5000,11 +5000,11 @@
         </is>
       </c>
       <c r="C61" s="50" t="n">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -5052,11 +5052,11 @@
         </is>
       </c>
       <c r="C62" s="50" t="n">
-        <v>46220</v>
+        <v>46222</v>
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -5104,11 +5104,11 @@
         </is>
       </c>
       <c r="C63" s="51" t="n">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="D63" s="27" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
@@ -5156,11 +5156,11 @@
         </is>
       </c>
       <c r="C64" s="51" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="D64" s="27" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
@@ -5208,11 +5208,11 @@
         </is>
       </c>
       <c r="C65" s="50" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -5264,11 +5264,11 @@
         </is>
       </c>
       <c r="C66" s="50" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -5320,11 +5320,11 @@
         </is>
       </c>
       <c r="C67" s="50" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -5376,11 +5376,11 @@
         </is>
       </c>
       <c r="C68" s="50" t="n">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -5432,11 +5432,11 @@
         </is>
       </c>
       <c r="C69" s="50" t="n">
-        <v>46227</v>
+        <v>46229</v>
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -5488,11 +5488,11 @@
         </is>
       </c>
       <c r="C70" s="51" t="n">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="D70" s="27" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -5544,11 +5544,11 @@
         </is>
       </c>
       <c r="C71" s="51" t="n">
-        <v>46229</v>
+        <v>46231</v>
       </c>
       <c r="D71" s="27" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
@@ -5600,11 +5600,11 @@
         </is>
       </c>
       <c r="C72" s="52" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="D72" s="29" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -5656,11 +5656,11 @@
         </is>
       </c>
       <c r="C73" s="52" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="D73" s="29" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -5708,11 +5708,11 @@
         </is>
       </c>
       <c r="C74" s="52" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="D74" s="29" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -5760,11 +5760,11 @@
         </is>
       </c>
       <c r="C75" s="52" t="n">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="D75" s="29" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -5812,11 +5812,11 @@
         </is>
       </c>
       <c r="C76" s="52" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="D76" s="29" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -5864,11 +5864,11 @@
         </is>
       </c>
       <c r="C77" s="53" t="n">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="D77" s="31" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
@@ -5916,11 +5916,11 @@
         </is>
       </c>
       <c r="C78" s="53" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
       <c r="D78" s="31" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
@@ -5968,11 +5968,11 @@
         </is>
       </c>
       <c r="C79" s="52" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="D79" s="29" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -6024,11 +6024,11 @@
         </is>
       </c>
       <c r="C80" s="52" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="D80" s="29" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -6080,11 +6080,11 @@
         </is>
       </c>
       <c r="C81" s="52" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="D81" s="29" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -6136,11 +6136,11 @@
         </is>
       </c>
       <c r="C82" s="52" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -6192,11 +6192,11 @@
         </is>
       </c>
       <c r="C83" s="52" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="D83" s="29" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -6248,11 +6248,11 @@
         </is>
       </c>
       <c r="C84" s="53" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="D84" s="31" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
@@ -6304,11 +6304,11 @@
         </is>
       </c>
       <c r="C85" s="53" t="n">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="D85" s="31" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
@@ -6360,11 +6360,11 @@
         </is>
       </c>
       <c r="C86" s="54" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="D86" s="33" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -6412,11 +6412,11 @@
         </is>
       </c>
       <c r="C87" s="54" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="D87" s="33" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -6464,11 +6464,11 @@
         </is>
       </c>
       <c r="C88" s="54" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="D88" s="33" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -6516,11 +6516,11 @@
         </is>
       </c>
       <c r="C89" s="54" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="D89" s="33" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -6568,11 +6568,11 @@
         </is>
       </c>
       <c r="C90" s="54" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="D90" s="33" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -6620,11 +6620,11 @@
         </is>
       </c>
       <c r="C91" s="55" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="D91" s="35" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
@@ -6672,11 +6672,11 @@
         </is>
       </c>
       <c r="C92" s="55" t="n">
-        <v>46250</v>
+        <v>46252</v>
       </c>
       <c r="D92" s="35" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
@@ -6724,11 +6724,11 @@
         </is>
       </c>
       <c r="C93" s="56" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="D93" s="37" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -6780,11 +6780,11 @@
         </is>
       </c>
       <c r="C94" s="56" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="D94" s="37" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -6836,11 +6836,11 @@
         </is>
       </c>
       <c r="C95" s="56" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="D95" s="37" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -6892,11 +6892,11 @@
         </is>
       </c>
       <c r="C96" s="56" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="D96" s="37" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -6948,11 +6948,11 @@
         </is>
       </c>
       <c r="C97" s="56" t="n">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="D97" s="37" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -7004,11 +7004,11 @@
         </is>
       </c>
       <c r="C98" s="57" t="n">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="D98" s="39" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
@@ -7060,11 +7060,11 @@
         </is>
       </c>
       <c r="C99" s="57" t="n">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="D99" s="39" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
